--- a/xlsx/Power/p6.xlsx
+++ b/xlsx/Power/p6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20255B93-1836-4DD4-8D2F-0378B1F03CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF90491-B2D8-4A1E-B657-A4457A658CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.317</v>
       </c>
       <c r="C1">
-        <v>0.46800000000000003</v>
+        <v>8.8999999999999996E-2</v>
       </c>
       <c r="D1">
-        <v>0.57399999999999995</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="E1">
-        <v>0.69</v>
+        <v>0.42899999999999999</v>
       </c>
       <c r="F1">
-        <v>0.754</v>
+        <v>0.56200000000000006</v>
       </c>
       <c r="G1">
-        <v>0.82899999999999996</v>
+        <v>0.69699999999999995</v>
       </c>
       <c r="H1">
-        <v>0.89</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I1">
-        <v>0.92200000000000004</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="J1">
-        <v>0.94099999999999995</v>
+        <v>0.88600000000000001</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.314</v>
       </c>
       <c r="C2">
-        <v>0.44900000000000001</v>
+        <v>9.9000000000000005E-2</v>
       </c>
       <c r="D2">
-        <v>0.56000000000000005</v>
+        <v>0.254</v>
       </c>
       <c r="E2">
-        <v>0.67</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="F2">
-        <v>0.74099999999999999</v>
+        <v>0.55800000000000005</v>
       </c>
       <c r="G2">
-        <v>0.81200000000000006</v>
+        <v>0.69299999999999995</v>
       </c>
       <c r="H2">
-        <v>0.87</v>
+        <v>0.76700000000000002</v>
       </c>
       <c r="I2">
-        <v>0.90600000000000003</v>
+        <v>0.84099999999999997</v>
       </c>
       <c r="J2">
-        <v>0.92900000000000005</v>
+        <v>0.877</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,22 +468,22 @@
         <v>0.27100000000000002</v>
       </c>
       <c r="C3">
-        <v>0.39500000000000002</v>
+        <v>0.45</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="E3">
-        <v>0.59499999999999997</v>
+        <v>0.59899999999999998</v>
       </c>
       <c r="F3">
-        <v>0.66800000000000004</v>
+        <v>0.67100000000000004</v>
       </c>
       <c r="G3">
-        <v>0.745</v>
+        <v>0.746</v>
       </c>
       <c r="H3">
-        <v>0.80400000000000005</v>
+        <v>0.80500000000000005</v>
       </c>
       <c r="I3">
         <v>0.86199999999999999</v>
@@ -494,34 +494,34 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14000000000000001</v>
+        <v>0.156</v>
       </c>
       <c r="B4">
-        <v>0.25</v>
+        <v>0.25800000000000001</v>
       </c>
       <c r="C4">
-        <v>0.35199999999999998</v>
+        <v>0.35799999999999998</v>
       </c>
       <c r="D4">
-        <v>0.45</v>
+        <v>0.44600000000000001</v>
       </c>
       <c r="E4">
         <v>0.52700000000000002</v>
       </c>
       <c r="F4">
-        <v>0.60899999999999999</v>
+        <v>0.61099999999999999</v>
       </c>
       <c r="G4">
         <v>0.68500000000000005</v>
       </c>
       <c r="H4">
-        <v>0.755</v>
+        <v>0.75</v>
       </c>
       <c r="I4">
-        <v>0.79600000000000004</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="J4">
-        <v>0.84399999999999997</v>
+        <v>0.84699999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,16 +532,16 @@
         <v>0.76200000000000001</v>
       </c>
       <c r="C5">
-        <v>0.92400000000000004</v>
+        <v>0.26700000000000002</v>
       </c>
       <c r="D5">
-        <v>0.97</v>
+        <v>0.76300000000000001</v>
       </c>
       <c r="E5">
-        <v>0.98799999999999999</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="F5">
-        <v>0.999</v>
+        <v>0.995</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -564,28 +564,28 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="C6">
-        <v>0.41699999999999998</v>
+        <v>0.58799999999999997</v>
       </c>
       <c r="D6">
-        <v>0.52700000000000002</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="E6">
-        <v>0.61199999999999999</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="F6">
-        <v>0.69199999999999995</v>
+        <v>0.71599999999999997</v>
       </c>
       <c r="G6">
-        <v>0.78800000000000003</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="H6">
-        <v>0.83599999999999997</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="I6">
         <v>0.89500000000000002</v>
       </c>
       <c r="J6">
-        <v>0.89900000000000002</v>
+        <v>0.91200000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="C7">
-        <v>0.40200000000000002</v>
+        <v>0.39700000000000002</v>
       </c>
       <c r="D7">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="E7">
-        <v>0.58499999999999996</v>
+        <v>0.59</v>
       </c>
       <c r="F7">
-        <v>0.66300000000000003</v>
+        <v>0.66100000000000003</v>
       </c>
       <c r="G7">
-        <v>0.747</v>
+        <v>0.74299999999999999</v>
       </c>
       <c r="H7">
         <v>0.8</v>
       </c>
       <c r="I7">
-        <v>0.86</v>
+        <v>0.85499999999999998</v>
       </c>
       <c r="J7">
-        <v>0.88400000000000001</v>
+        <v>0.88200000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.183</v>
       </c>
       <c r="C8">
-        <v>0.25700000000000001</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.31</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="E8">
-        <v>0.40500000000000003</v>
+        <v>0.16300000000000001</v>
       </c>
       <c r="F8">
-        <v>0.46500000000000002</v>
+        <v>0.23</v>
       </c>
       <c r="G8">
-        <v>0.51700000000000002</v>
+        <v>0.33600000000000002</v>
       </c>
       <c r="H8">
-        <v>0.57499999999999996</v>
+        <v>0.41799999999999998</v>
       </c>
       <c r="I8">
-        <v>0.69799999999999995</v>
+        <v>0.23899999999999999</v>
       </c>
       <c r="J8">
-        <v>0.71199999999999997</v>
+        <v>0.27500000000000002</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="C9">
-        <v>0.13600000000000001</v>
+        <v>0.42199999999999999</v>
       </c>
       <c r="D9">
-        <v>0.158</v>
+        <v>0.89400000000000002</v>
       </c>
       <c r="E9">
-        <v>0.20100000000000001</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="F9">
-        <v>0.26300000000000001</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="G9">
-        <v>0.27100000000000002</v>
+        <v>0.34899999999999998</v>
       </c>
       <c r="H9">
-        <v>0.32300000000000001</v>
+        <v>0.36399999999999999</v>
       </c>
       <c r="I9">
-        <v>0.38100000000000001</v>
+        <v>0.40400000000000003</v>
       </c>
       <c r="J9">
-        <v>0.41399999999999998</v>
+        <v>0.437</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p6.xlsx
+++ b/xlsx/Power/p6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF90491-B2D8-4A1E-B657-A4457A658CAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF603C5-B64D-440F-A3A1-ECC4D90A9CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
+    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -404,28 +404,28 @@
         <v>0.317</v>
       </c>
       <c r="C1">
-        <v>8.8999999999999996E-2</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="D1">
-        <v>0.24299999999999999</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="E1">
-        <v>0.42899999999999999</v>
+        <v>0.69</v>
       </c>
       <c r="F1">
-        <v>0.56200000000000006</v>
+        <v>0.754</v>
       </c>
       <c r="G1">
-        <v>0.69699999999999995</v>
+        <v>0.82899999999999996</v>
       </c>
       <c r="H1">
-        <v>0.77500000000000002</v>
+        <v>0.89</v>
       </c>
       <c r="I1">
-        <v>0.86299999999999999</v>
+        <v>0.92200000000000004</v>
       </c>
       <c r="J1">
-        <v>0.88600000000000001</v>
+        <v>0.94099999999999995</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -436,28 +436,28 @@
         <v>0.314</v>
       </c>
       <c r="C2">
-        <v>9.9000000000000005E-2</v>
+        <v>0.44900000000000001</v>
       </c>
       <c r="D2">
-        <v>0.254</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="E2">
-        <v>0.41799999999999998</v>
+        <v>0.67</v>
       </c>
       <c r="F2">
-        <v>0.55800000000000005</v>
+        <v>0.74099999999999999</v>
       </c>
       <c r="G2">
-        <v>0.69299999999999995</v>
+        <v>0.81200000000000006</v>
       </c>
       <c r="H2">
-        <v>0.76700000000000002</v>
+        <v>0.87</v>
       </c>
       <c r="I2">
-        <v>0.84099999999999997</v>
+        <v>0.90600000000000003</v>
       </c>
       <c r="J2">
-        <v>0.877</v>
+        <v>0.92900000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -468,22 +468,22 @@
         <v>0.27100000000000002</v>
       </c>
       <c r="C3">
-        <v>0.45</v>
+        <v>0.39500000000000002</v>
       </c>
       <c r="D3">
-        <v>0.51200000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="E3">
-        <v>0.59899999999999998</v>
+        <v>0.59499999999999997</v>
       </c>
       <c r="F3">
-        <v>0.67100000000000004</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="G3">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="H3">
-        <v>0.80500000000000005</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="I3">
         <v>0.86199999999999999</v>
@@ -494,34 +494,34 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.156</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="B4">
-        <v>0.25800000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="C4">
-        <v>0.35799999999999998</v>
+        <v>0.35199999999999998</v>
       </c>
       <c r="D4">
-        <v>0.44600000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="E4">
         <v>0.52700000000000002</v>
       </c>
       <c r="F4">
-        <v>0.61099999999999999</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="G4">
         <v>0.68500000000000005</v>
       </c>
       <c r="H4">
-        <v>0.75</v>
+        <v>0.755</v>
       </c>
       <c r="I4">
-        <v>0.79500000000000004</v>
+        <v>0.79600000000000004</v>
       </c>
       <c r="J4">
-        <v>0.84699999999999998</v>
+        <v>0.84399999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -532,16 +532,16 @@
         <v>0.76200000000000001</v>
       </c>
       <c r="C5">
-        <v>0.26700000000000002</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="D5">
-        <v>0.76300000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="E5">
-        <v>0.93200000000000005</v>
+        <v>0.98799999999999999</v>
       </c>
       <c r="F5">
-        <v>0.995</v>
+        <v>0.999</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -564,28 +564,28 @@
         <v>0.30399999999999999</v>
       </c>
       <c r="C6">
-        <v>0.58799999999999997</v>
+        <v>0.41699999999999998</v>
       </c>
       <c r="D6">
-        <v>0.59599999999999997</v>
+        <v>0.52700000000000002</v>
       </c>
       <c r="E6">
-        <v>0.66200000000000003</v>
+        <v>0.61199999999999999</v>
       </c>
       <c r="F6">
-        <v>0.71599999999999997</v>
+        <v>0.69199999999999995</v>
       </c>
       <c r="G6">
-        <v>0.79600000000000004</v>
+        <v>0.78800000000000003</v>
       </c>
       <c r="H6">
-        <v>0.83799999999999997</v>
+        <v>0.83599999999999997</v>
       </c>
       <c r="I6">
         <v>0.89500000000000002</v>
       </c>
       <c r="J6">
-        <v>0.91200000000000003</v>
+        <v>0.89900000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -596,28 +596,28 @@
         <v>0.29099999999999998</v>
       </c>
       <c r="C7">
-        <v>0.39700000000000002</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="D7">
-        <v>0.498</v>
+        <v>0.499</v>
       </c>
       <c r="E7">
-        <v>0.59</v>
+        <v>0.58499999999999996</v>
       </c>
       <c r="F7">
-        <v>0.66100000000000003</v>
+        <v>0.66200000000000003</v>
       </c>
       <c r="G7">
-        <v>0.74299999999999999</v>
+        <v>0.746</v>
       </c>
       <c r="H7">
         <v>0.8</v>
       </c>
       <c r="I7">
-        <v>0.85499999999999998</v>
+        <v>0.86</v>
       </c>
       <c r="J7">
-        <v>0.88200000000000001</v>
+        <v>0.88400000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -628,28 +628,28 @@
         <v>0.183</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="D8">
-        <v>4.8000000000000001E-2</v>
+        <v>0.31</v>
       </c>
       <c r="E8">
-        <v>0.16300000000000001</v>
+        <v>0.40500000000000003</v>
       </c>
       <c r="F8">
-        <v>0.23</v>
+        <v>0.46500000000000002</v>
       </c>
       <c r="G8">
-        <v>0.33600000000000002</v>
+        <v>0.51700000000000002</v>
       </c>
       <c r="H8">
-        <v>0.41799999999999998</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="I8">
-        <v>0.23899999999999999</v>
+        <v>0.69799999999999995</v>
       </c>
       <c r="J8">
-        <v>0.27500000000000002</v>
+        <v>0.71199999999999997</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -660,28 +660,28 @@
         <v>0.17199999999999999</v>
       </c>
       <c r="C9">
-        <v>0.42199999999999999</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="D9">
-        <v>0.89400000000000002</v>
+        <v>0.158</v>
       </c>
       <c r="E9">
-        <v>0.72299999999999998</v>
+        <v>0.20100000000000001</v>
       </c>
       <c r="F9">
-        <v>0.39400000000000002</v>
+        <v>0.26300000000000001</v>
       </c>
       <c r="G9">
-        <v>0.34899999999999998</v>
+        <v>0.27100000000000002</v>
       </c>
       <c r="H9">
-        <v>0.36399999999999999</v>
+        <v>0.32300000000000001</v>
       </c>
       <c r="I9">
-        <v>0.40400000000000003</v>
+        <v>0.38100000000000001</v>
       </c>
       <c r="J9">
-        <v>0.437</v>
+        <v>0.41399999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Power/p6.xlsx
+++ b/xlsx/Power/p6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEF603C5-B64D-440F-A3A1-ECC4D90A9CB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0DB260-9007-4F35-A242-2258612AB696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{59E7D556-6DE4-4305-BEC9-1F89B5F927A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Munka1" sheetId="1" r:id="rId1"/>
@@ -398,22 +398,22 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1">
-        <v>0.16200000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="B1">
         <v>0.317</v>
       </c>
       <c r="C1">
-        <v>0.46800000000000003</v>
+        <v>0.46899999999999997</v>
       </c>
       <c r="D1">
-        <v>0.57399999999999995</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="E1">
         <v>0.69</v>
       </c>
       <c r="F1">
-        <v>0.754</v>
+        <v>0.755</v>
       </c>
       <c r="G1">
         <v>0.82899999999999996</v>
@@ -422,7 +422,7 @@
         <v>0.89</v>
       </c>
       <c r="I1">
-        <v>0.92200000000000004</v>
+        <v>0.92400000000000004</v>
       </c>
       <c r="J1">
         <v>0.94099999999999995</v>
@@ -430,176 +430,176 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.159</v>
+        <v>0.157</v>
       </c>
       <c r="B2">
-        <v>0.314</v>
+        <v>0.316</v>
       </c>
       <c r="C2">
         <v>0.44900000000000001</v>
       </c>
       <c r="D2">
-        <v>0.56000000000000005</v>
+        <v>0.55900000000000005</v>
       </c>
       <c r="E2">
-        <v>0.67</v>
+        <v>0.66800000000000004</v>
       </c>
       <c r="F2">
-        <v>0.74099999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="G2">
-        <v>0.81200000000000006</v>
+        <v>0.81</v>
       </c>
       <c r="H2">
-        <v>0.87</v>
+        <v>0.86699999999999999</v>
       </c>
       <c r="I2">
-        <v>0.90600000000000003</v>
+        <v>0.90900000000000003</v>
       </c>
       <c r="J2">
-        <v>0.92900000000000005</v>
+        <v>0.93100000000000005</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>0.153</v>
+        <v>0.14799999999999999</v>
       </c>
       <c r="B3">
-        <v>0.27100000000000002</v>
+        <v>0.27400000000000002</v>
       </c>
       <c r="C3">
-        <v>0.39500000000000002</v>
+        <v>0.40200000000000002</v>
       </c>
       <c r="D3">
-        <v>0.5</v>
+        <v>0.503</v>
       </c>
       <c r="E3">
-        <v>0.59499999999999997</v>
+        <v>0.59599999999999997</v>
       </c>
       <c r="F3">
         <v>0.66800000000000004</v>
       </c>
       <c r="G3">
-        <v>0.745</v>
+        <v>0.747</v>
       </c>
       <c r="H3">
-        <v>0.80400000000000005</v>
+        <v>0.80700000000000005</v>
       </c>
       <c r="I3">
-        <v>0.86199999999999999</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="J3">
-        <v>0.88400000000000001</v>
+        <v>0.89200000000000002</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>0.14000000000000001</v>
+        <v>0.13900000000000001</v>
       </c>
       <c r="B4">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="C4">
-        <v>0.35199999999999998</v>
+        <v>0.35599999999999998</v>
       </c>
       <c r="D4">
-        <v>0.45</v>
+        <v>0.45100000000000001</v>
       </c>
       <c r="E4">
-        <v>0.52700000000000002</v>
+        <v>0.53</v>
       </c>
       <c r="F4">
-        <v>0.60899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="G4">
-        <v>0.68500000000000005</v>
+        <v>0.68600000000000005</v>
       </c>
       <c r="H4">
-        <v>0.755</v>
+        <v>0.75900000000000001</v>
       </c>
       <c r="I4">
-        <v>0.79600000000000004</v>
+        <v>0.80400000000000005</v>
       </c>
       <c r="J4">
-        <v>0.84399999999999997</v>
+        <v>0.85099999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.46800000000000003</v>
+        <v>0</v>
       </c>
       <c r="B5">
-        <v>0.76200000000000001</v>
+        <v>6.0000000000000001E-3</v>
       </c>
       <c r="C5">
-        <v>0.92400000000000004</v>
+        <v>1.2E-2</v>
       </c>
       <c r="D5">
-        <v>0.97</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="E5">
-        <v>0.98799999999999999</v>
+        <v>2.9000000000000001E-2</v>
       </c>
       <c r="F5">
-        <v>0.999</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>8.2000000000000003E-2</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0.16300000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="B6">
         <v>0.30399999999999999</v>
       </c>
       <c r="C6">
-        <v>0.41699999999999998</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="D6">
-        <v>0.52700000000000002</v>
+        <v>0.52600000000000002</v>
       </c>
       <c r="E6">
-        <v>0.61199999999999999</v>
+        <v>0.60899999999999999</v>
       </c>
       <c r="F6">
-        <v>0.69199999999999995</v>
+        <v>0.68899999999999995</v>
       </c>
       <c r="G6">
-        <v>0.78800000000000003</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="H6">
-        <v>0.83599999999999997</v>
+        <v>0.83299999999999996</v>
       </c>
       <c r="I6">
-        <v>0.89500000000000002</v>
+        <v>0.89</v>
       </c>
       <c r="J6">
-        <v>0.89900000000000002</v>
+        <v>0.90300000000000002</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>0.159</v>
+        <v>0.157</v>
       </c>
       <c r="B7">
-        <v>0.29099999999999998</v>
+        <v>0.28899999999999998</v>
       </c>
       <c r="C7">
         <v>0.40200000000000002</v>
       </c>
       <c r="D7">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="E7">
         <v>0.58499999999999996</v>
@@ -608,7 +608,7 @@
         <v>0.66200000000000003</v>
       </c>
       <c r="G7">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="H7">
         <v>0.8</v>
@@ -617,7 +617,7 @@
         <v>0.86</v>
       </c>
       <c r="J7">
-        <v>0.88400000000000001</v>
+        <v>0.88300000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -634,10 +634,10 @@
         <v>0.31</v>
       </c>
       <c r="E8">
-        <v>0.40500000000000003</v>
+        <v>0.41099999999999998</v>
       </c>
       <c r="F8">
-        <v>0.46500000000000002</v>
+        <v>0.46800000000000003</v>
       </c>
       <c r="G8">
         <v>0.51700000000000002</v>
@@ -646,7 +646,7 @@
         <v>0.57499999999999996</v>
       </c>
       <c r="I8">
-        <v>0.69799999999999995</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="J8">
         <v>0.71199999999999997</v>
@@ -654,34 +654,34 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.113</v>
+        <v>0.114</v>
       </c>
       <c r="B9">
-        <v>0.17199999999999999</v>
+        <v>0.17599999999999999</v>
       </c>
       <c r="C9">
-        <v>0.13600000000000001</v>
+        <v>0.13700000000000001</v>
       </c>
       <c r="D9">
         <v>0.158</v>
       </c>
       <c r="E9">
-        <v>0.20100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F9">
         <v>0.26300000000000001</v>
       </c>
       <c r="G9">
-        <v>0.27100000000000002</v>
+        <v>0.26800000000000002</v>
       </c>
       <c r="H9">
-        <v>0.32300000000000001</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="I9">
-        <v>0.38100000000000001</v>
+        <v>0.38200000000000001</v>
       </c>
       <c r="J9">
-        <v>0.41399999999999998</v>
+        <v>0.41899999999999998</v>
       </c>
     </row>
   </sheetData>
